--- a/docs/cost_model.xlsx
+++ b/docs/cost_model.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="207">
   <si>
     <t xml:space="preserve">myFamiPedia — Cost Model Assumptions</t>
   </si>
@@ -307,6 +307,63 @@
     <t xml:space="preserve">Illustrative — assumes you raise prices over time (inflation tracking or value capture), not that €12-15/€99-120 stays fixed for a decade. Adjust to 0% to model flat pricing.</t>
   </si>
   <si>
+    <t xml:space="preserve">Scene classification (photo pipeline v2) — added 2026-07-18, see docs/photo_pipeline_beta_architecture.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Rekognition DetectLabels (Group 2, tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aws.amazon.com/rekognition/pricing — same Group 2 tier-1 rate as DetectFaces, first 1M images/month tier (fetched Jul 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude Haiku 4.5 — input tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platform.claude.com/docs/en/about-claude/pricing (fetched Jul 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude Haiku 4.5 — output tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude vision — image tokens per pixel (divisor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pixels per token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthropic vision docs: tokens ≈ width×height/750 (fetched Jul 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg output tokens per Haiku caption suggestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative — short one-sentence caption, not measured data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos processed by Rekognition DetectLabels (stage 1) per active user per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/user/month — per your estimate (2026-07-18). Separate from the primary "Photos uploaded" driver on row 31 — not reconciled, see Notes &amp; Sources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New photos processed per month (family total) — DetectLabels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: photos/user/month x family size (row 29). Feeds Rekognition DetectLabels cost below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos requiring Claude Haiku review (stage 2) per active user per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/user/month — per your estimate (2026-07-18); 10 of the 50 DetectLabels photos, i.e. 20% triage-pass rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New photos processed per month (family total) — Haiku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: photos/user/month x family size (row 29). Feeds Claude Haiku cost below.</t>
+  </si>
+  <si>
     <t xml:space="preserve">myFamiPedia — Per-Family Monthly Cost (EUR)</t>
   </si>
   <si>
@@ -391,6 +448,15 @@
     <t xml:space="preserve">Annual plan vs. target (pp)</t>
   </si>
   <si>
+    <t xml:space="preserve">Scene classification (photo pipeline v2) — added 2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekognition DetectLabels (scene classification, stage 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude Haiku (scene classification, stage 2 — caption + confirm)</t>
+  </si>
+  <si>
     <t xml:space="preserve">myFamiPedia — Scale Scenarios (EUR, Year 5 usage basis)</t>
   </si>
   <si>
@@ -560,6 +626,24 @@
   </si>
   <si>
     <t xml:space="preserve">These two levers pull margin in opposite directions from the previous (static-price) version: costs shrink over the decade instead of just growing with usage, and revenue grows instead of staying flat — both improve Year 10 margin relative to the prior version. Check the Per-Family Monthly Cost sheet's Year 10 margin lines to see the current net result with the default -10%/+3% assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scene classification (photo pipeline v2, added 2026-07-18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-stage design: AWS Rekognition DetectLabels runs on every photo processed by the pipeline (cheap triage, same Group 2 tier-1 rate as DetectFaces); Claude Haiku 4.5 runs only on the photos that pass triage, to write the caption suggestion and confirm/veto candidate-worthiness. See docs/photo_pipeline_beta_architecture.md section 5 for the full design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scene-classification photo volume, not reconciled with the main driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions!B63 (50 photos/user/month through DetectLabels) and B65 (10/user/month through Haiku) are your own estimates (2026-07-18), entered separately from the primary "Photos uploaded per active user per month" driver (row 31, 20/user/month) that feeds storage, Voyage-image embedding, and the other Rekognition lines. The two aren't reconciled — 50 through classification is more than the 20 assumed to be uploaded at all. Surfaced, not silently fixed, same convention as the storage cross-check gap above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekognition SearchFacesByImage / face vector storage — flagged, not changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-Family Monthly Cost rows 11-12 still cost out AWS Rekognition SearchFacesByImage and face vector storage — the automated face-matching/enrollment pipeline. That pipeline was disabled at the code level on 2026-07-18 (GDPR Article 9 exposure, see docs/family_administrator_and_privacy_model.md section 5) and has no replacement that calls those APIs in the redesigned architecture (docs/photo_pipeline_beta_architecture.md). Left as-is here rather than removed unilaterally — flagging that this model currently overstates cost (and understates margin) by budgeting for a feature that no longer runs, pending a decision on whether to zero out or delete those two lines.</t>
   </si>
 </sst>
 </file>
@@ -702,7 +786,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -763,18 +847,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -809,10 +881,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1067,7 +1135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -1625,48 +1693,228 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="10" t="n">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B50" s="17" t="n">
+      <c r="B50" s="8" t="n">
         <v>-0.1</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="17" t="n">
+      <c r="B51" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="13" t="n">
+        <f aca="false">B63*B29</f>
+        <v>1000</v>
+      </c>
+      <c r="C64" s="13" t="n">
+        <f aca="false">C63*C29</f>
+        <v>1000</v>
+      </c>
+      <c r="D64" s="13" t="n">
+        <f aca="false">D63*D29</f>
+        <v>1000</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="13" t="n">
+        <f aca="false">B65*B29</f>
+        <v>200</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <f aca="false">C65*C29</f>
+        <v>200</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <f aca="false">D65*D29</f>
+        <v>200</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1933,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54"/>
@@ -1694,172 +1942,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="15" t="n">
         <f aca="false">Assumptions!$B$30*Assumptions!$B$9*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.14904</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="15" t="n">
         <f aca="false">Assumptions!$C$30*Assumptions!$B$9*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.44818191</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="15" t="n">
         <f aca="false">Assumptions!$D$30*Assumptions!$B$9*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.5292938720718</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="B5" s="15" t="n">
         <f aca="false">(Assumptions!$B$41*Assumptions!$B$10/1000000+Assumptions!$B$42*Assumptions!$B$11/1000000)*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.001941246</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="15" t="n">
         <f aca="false">(Assumptions!$C$41*Assumptions!$B$10/1000000+Assumptions!$C$42*Assumptions!$B$11/1000000)*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.0012272035572</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="15" t="n">
         <f aca="false">(Assumptions!$D$41*Assumptions!$B$10/1000000+Assumptions!$D$42*Assumptions!$B$11/1000000)*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.000700400145625193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="18" t="n">
+        <v>119</v>
+      </c>
+      <c r="B6" s="15" t="n">
         <f aca="false">Assumptions!$B$35*Assumptions!$B$14*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.07452</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="15" t="n">
         <f aca="false">Assumptions!$C$35*Assumptions!$B$14*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.032595048</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="15" t="n">
         <f aca="false">Assumptions!$D$35*Assumptions!$B$14*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.00962352494676</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="18" t="n">
+        <v>120</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <f aca="false">Assumptions!$B$38/1000*Assumptions!$B$15*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.0414</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="15" t="n">
         <f aca="false">Assumptions!$C$38/1000*Assumptions!$B$15*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.10865016</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="15" t="n">
         <f aca="false">Assumptions!$D$38/1000*Assumptions!$B$15*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.1283136659568</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="18" t="n">
+        <v>121</v>
+      </c>
+      <c r="B8" s="15" t="n">
         <f aca="false">(Assumptions!$B$36*Assumptions!$B$37)/1000000*Assumptions!$B$12*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.000357696</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="15" t="n">
         <f aca="false">(Assumptions!$C$36*Assumptions!$C$37)/1000000*Assumptions!$B$12*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.0001564562304</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="15" t="n">
         <f aca="false">(Assumptions!$D$36*Assumptions!$D$37)/1000000*Assumptions!$B$12*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>5.54315036933376E-005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="18" t="n">
+        <v>122</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">(Assumptions!$B$32*Assumptions!$B$34)/1000000000*Assumptions!$B$13*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.39744</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="15" t="n">
         <f aca="false">(Assumptions!$C$32*Assumptions!$C$34)/1000000000*Assumptions!$B$13*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.260760384</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="15" t="n">
         <f aca="false">(Assumptions!$D$32*Assumptions!$D$34)/1000000000*Assumptions!$B$13*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.15397639914816</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="18" t="n">
+        <v>123</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <f aca="false">Assumptions!$B$32*Assumptions!$B$16*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.3312</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="15" t="n">
         <f aca="false">Assumptions!$C$32*Assumptions!$B$16*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.21730032</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="15" t="n">
         <f aca="false">Assumptions!$D$32*Assumptions!$B$16*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.1283136659568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="18" t="n">
+        <v>124</v>
+      </c>
+      <c r="B11" s="15" t="n">
         <f aca="false">Assumptions!$B$32*Assumptions!$B$17*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.3312</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="15" t="n">
         <f aca="false">Assumptions!$C$32*Assumptions!$B$17*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.21730032</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="15" t="n">
         <f aca="false">Assumptions!$D$32*Assumptions!$B$17*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.1283136659568</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="18" t="n">
+        <v>125</v>
+      </c>
+      <c r="B12" s="15" t="n">
         <f aca="false">Assumptions!$B$40*Assumptions!$B$18*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.0001656</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="15" t="n">
         <f aca="false">Assumptions!$C$40*Assumptions!$B$18*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.00010865016</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="15" t="n">
         <f aca="false">Assumptions!$D$40*Assumptions!$B$18*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>6.41568329784E-005</v>
       </c>
@@ -1868,226 +2116,226 @@
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="15" t="n">
         <f aca="false">Assumptions!$B$39/1000000*Assumptions!$B$19*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.0207</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="15" t="n">
         <f aca="false">Assumptions!$C$39/1000000*Assumptions!$B$19*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.01358127</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="15" t="n">
         <f aca="false">Assumptions!$D$39/1000000*Assumptions!$B$19*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.0080196041223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="19" t="n">
-        <f aca="false">SUM(B4:B13)</f>
-        <v>1.347964542</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <f aca="false">SUM(C4:C13)</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <f aca="false">SUM(D4:D13)</f>
-        <v>1.08667438664172</v>
+        <v>126</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">SUM(B4:B13)+B37+B38</f>
+        <v>2.667244542</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">SUM(C4:C13)+C37+C38</f>
+        <v>2.1654413299476</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">SUM(D4:D13)+D37+D38</f>
+        <v>1.59779048936964</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="18" t="n">
+        <v>127</v>
+      </c>
+      <c r="B16" s="15" t="n">
         <f aca="false">INDEX('Scale Scenarios'!$D:$D,MATCH(Assumptions!$B$45,'Scale Scenarios'!$A:$A,0))*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.00831173724</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="15" t="n">
         <f aca="false">INDEX('Scale Scenarios'!$D:$D,MATCH(Assumptions!$B$45,'Scale Scenarios'!$A:$A,0))*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.005453330803164</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="15" t="n">
         <f aca="false">INDEX('Scale Scenarios'!$D:$D,MATCH(Assumptions!$B$45,'Scale Scenarios'!$A:$A,0))*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.00322013730596031</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="18" t="n">
+        <v>128</v>
+      </c>
+      <c r="B17" s="15" t="n">
         <f aca="false">INDEX('Scale Scenarios'!$E:$E,MATCH(Assumptions!$B$45,'Scale Scenarios'!$A:$A,0))*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
         <v>0.0053684044056</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="15" t="n">
         <f aca="false">INDEX('Scale Scenarios'!$E:$E,MATCH(Assumptions!$B$45,'Scale Scenarios'!$A:$A,0))*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.00352221013051416</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="15" t="n">
         <f aca="false">INDEX('Scale Scenarios'!$E:$E,MATCH(Assumptions!$B$45,'Scale Scenarios'!$A:$A,0))*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
         <v>0.00207982985996731</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="19" t="n">
+        <v>129</v>
+      </c>
+      <c r="B18" s="16" t="n">
         <f aca="false">SUM(B16:B17)</f>
         <v>0.0136801416456</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="16" t="n">
         <f aca="false">SUM(C16:C17)</f>
         <v>0.00897554093367816</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="16" t="n">
         <f aca="false">SUM(D16:D17)</f>
         <v>0.00529996716592762</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="B20" s="16" t="n">
         <f aca="false">B14+B18</f>
-        <v>1.3616446836456</v>
-      </c>
-      <c r="C20" s="19" t="n">
+        <v>2.6809246836456</v>
+      </c>
+      <c r="C20" s="16" t="n">
         <f aca="false">C14+C18</f>
-        <v>1.30883726288128</v>
-      </c>
-      <c r="D20" s="19" t="n">
+        <v>2.17441687088128</v>
+      </c>
+      <c r="D20" s="16" t="n">
         <f aca="false">D14+D18</f>
-        <v>1.09197435380764</v>
+        <v>1.60309045653557</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B21" s="12" t="str">
-        <f aca="false">INDEX($A$4:$A$13,MATCH(MAX(B4:B13),B4:B13,0))</f>
-        <v>Voyage embeddings — image (photos)</v>
+        <f aca="false">IF(MAX(B37,B38)&gt;MAX(B4:B13),IF(B37&gt;B38,$A$37,$A$38),INDEX($A$4:$A$13,MATCH(MAX(B4:B13),B4:B13,0)))</f>
+        <v>Rekognition DetectLabels (scene classification, stage 1)</v>
       </c>
       <c r="C21" s="12" t="str">
-        <f aca="false">INDEX($A$4:$A$13,MATCH(MAX(C4:C13),C4:C13,0))</f>
-        <v>R2 storage</v>
+        <f aca="false">IF(MAX(C37,C38)&gt;MAX(C4:C13),IF(C37&gt;C38,$A$37,$A$38),INDEX($A$4:$A$13,MATCH(MAX(C4:C13),C4:C13,0)))</f>
+        <v>Rekognition DetectLabels (scene classification, stage 1)</v>
       </c>
       <c r="D21" s="12" t="str">
-        <f aca="false">INDEX($A$4:$A$13,MATCH(MAX(D4:D13),D4:D13,0))</f>
+        <f aca="false">IF(MAX(D37,D38)&gt;MAX(D4:D13),IF(D37&gt;D38,$A$37,$A$38),INDEX($A$4:$A$13,MATCH(MAX(D4:D13),D4:D13,0)))</f>
         <v>R2 storage</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B23" s="17" t="n">
         <f aca="false">13.5*(1+Assumptions!$B$51)^Assumptions!$B$49</f>
         <v>13.905</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="17" t="n">
         <f aca="false">13.5*(1+Assumptions!$B$51)^Assumptions!$C$49</f>
         <v>15.65020000305</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="17" t="n">
         <f aca="false">13.5*(1+Assumptions!$B$51)^Assumptions!$D$49</f>
         <v>18.1428711211457</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="20" t="n">
+        <v>133</v>
+      </c>
+      <c r="B24" s="17" t="n">
         <f aca="false">(109.5/12)*(1+Assumptions!$B$51)^Assumptions!$B$49</f>
         <v>9.39875</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="17" t="n">
         <f aca="false">(109.5/12)*(1+Assumptions!$B$51)^Assumptions!$C$49</f>
         <v>10.5783759279875</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">(109.5/12)*(1+Assumptions!$B$51)^Assumptions!$D$49</f>
         <v>12.2632369615151</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" s="18" t="n">
+        <v>134</v>
+      </c>
+      <c r="B26" s="15" t="n">
         <f aca="false">B23-B20</f>
-        <v>12.5433553163544</v>
-      </c>
-      <c r="C26" s="18" t="n">
+        <v>11.2240753163544</v>
+      </c>
+      <c r="C26" s="15" t="n">
         <f aca="false">C23-C20</f>
-        <v>14.3413627401687</v>
-      </c>
-      <c r="D26" s="18" t="n">
+        <v>13.4757831321687</v>
+      </c>
+      <c r="D26" s="15" t="n">
         <f aca="false">D23-D20</f>
-        <v>17.050896767338</v>
+        <v>16.5397806646101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="21" t="n">
+        <v>135</v>
+      </c>
+      <c r="B27" s="18" t="n">
         <f aca="false">B26/B23</f>
-        <v>0.902075175573851</v>
-      </c>
-      <c r="C27" s="21" t="n">
+        <v>0.807197074171478</v>
+      </c>
+      <c r="C27" s="18" t="n">
         <f aca="false">C26/C23</f>
-        <v>0.91636929479328</v>
-      </c>
-      <c r="D27" s="21" t="n">
+        <v>0.861061400464051</v>
+      </c>
+      <c r="D27" s="18" t="n">
         <f aca="false">D26/D23</f>
-        <v>0.939812483563589</v>
+        <v>0.911640751575028</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="18" t="n">
+        <v>136</v>
+      </c>
+      <c r="B29" s="15" t="n">
         <f aca="false">B24-B20</f>
-        <v>8.0371053163544</v>
-      </c>
-      <c r="C29" s="18" t="n">
+        <v>6.7178253163544</v>
+      </c>
+      <c r="C29" s="15" t="n">
         <f aca="false">C24-C20</f>
-        <v>9.26953866510622</v>
-      </c>
-      <c r="D29" s="18" t="n">
+        <v>8.40395905710622</v>
+      </c>
+      <c r="D29" s="15" t="n">
         <f aca="false">D24-D20</f>
-        <v>11.1712626077075</v>
+        <v>10.6601465049796</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="21" t="n">
+        <v>137</v>
+      </c>
+      <c r="B30" s="18" t="n">
         <f aca="false">B29/B24</f>
-        <v>0.855124917287341</v>
-      </c>
-      <c r="C30" s="21" t="n">
+        <v>0.714757315212597</v>
+      </c>
+      <c r="C30" s="18" t="n">
         <f aca="false">C29/C24</f>
-        <v>0.876272381338004</v>
-      </c>
-      <c r="D30" s="21" t="n">
+        <v>0.794447003426267</v>
+      </c>
+      <c r="D30" s="18" t="n">
         <f aca="false">D29/D24</f>
-        <v>0.910955455135172</v>
+        <v>0.869276728357575</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>0.775</v>
@@ -2101,36 +2349,75 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" s="21" t="n">
+        <v>139</v>
+      </c>
+      <c r="B33" s="18" t="n">
         <f aca="false">B27-B32</f>
-        <v>0.127075175573851</v>
-      </c>
-      <c r="C33" s="21" t="n">
+        <v>0.0321970741714779</v>
+      </c>
+      <c r="C33" s="18" t="n">
         <f aca="false">C27-C32</f>
-        <v>0.14136929479328</v>
-      </c>
-      <c r="D33" s="21" t="n">
+        <v>0.0860614004640505</v>
+      </c>
+      <c r="D33" s="18" t="n">
         <f aca="false">D27-D32</f>
-        <v>0.164812483563589</v>
+        <v>0.136640751575028</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="B34" s="18" t="n">
         <f aca="false">B30-B32</f>
-        <v>0.0801249172873413</v>
-      </c>
-      <c r="C34" s="21" t="n">
+        <v>-0.0602426847874026</v>
+      </c>
+      <c r="C34" s="18" t="n">
         <f aca="false">C30-C32</f>
-        <v>0.101272381338004</v>
-      </c>
-      <c r="D34" s="21" t="n">
+        <v>0.0194470034262666</v>
+      </c>
+      <c r="D34" s="18" t="n">
         <f aca="false">D30-D32</f>
-        <v>0.135955455135172</v>
+        <v>0.0942767283575752</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="15" t="n">
+        <f aca="false">Assumptions!$B$64*Assumptions!$B$55*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
+        <v>0.828</v>
+      </c>
+      <c r="C37" s="15" t="n">
+        <f aca="false">Assumptions!$C$64*Assumptions!$B$55*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
+        <v>0.5432508</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <f aca="false">Assumptions!$D$64*Assumptions!$B$55*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
+        <v>0.320784164892</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" s="15" t="n">
+        <f aca="false">Assumptions!$B$66*((Assumptions!$B$34/Assumptions!$B$59)/1000000*Assumptions!$B$56+Assumptions!$B$60/1000000*Assumptions!$B$57)*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$B$49</f>
+        <v>0.49128</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <f aca="false">Assumptions!$C$66*((Assumptions!$C$34/Assumptions!$B$59)/1000000*Assumptions!$B$56+Assumptions!$B$60/1000000*Assumptions!$B$57)*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
+        <v>0.322328808</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <f aca="false">Assumptions!$D$66*((Assumptions!$D$34/Assumptions!$B$59)/1000000*Assumptions!$B$56+Assumptions!$B$60/1000000*Assumptions!$B$57)*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$D$49</f>
+        <v>0.19033193783592</v>
       </c>
     </row>
   </sheetData>
@@ -2166,290 +2453,290 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="19" t="n">
         <f aca="false">CEILING(A5/Assumptions!$B$46,1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="15" t="n">
         <f aca="false">B5*Assumptions!$B$21*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>4.6176318</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="15" t="n">
         <f aca="false">C5/A5</f>
         <v>0.092352636</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="15" t="n">
         <f aca="false">Assumptions!$B$20*Assumptions!$B$5/A5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.05964893784</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="15" t="n">
         <f aca="false">D5+E5</f>
         <v>0.15200157384</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$14</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="H5" s="18" t="n">
+        <v>2.1654413299476</v>
+      </c>
+      <c r="H5" s="15" t="n">
         <f aca="false">F5+G5</f>
-        <v>1.4518632957876</v>
-      </c>
-      <c r="I5" s="18" t="n">
+        <v>2.3174429037876</v>
+      </c>
+      <c r="I5" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$23</f>
         <v>15.65020000305</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="18" t="n">
         <f aca="false">(I5-H5)/I5</f>
-        <v>0.907230367950272</v>
+        <v>0.851922473621042</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="19" t="n">
         <f aca="false">CEILING(A6/Assumptions!$B$46,1)</f>
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="15" t="n">
         <f aca="false">B6*Assumptions!$B$21*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>4.6176318</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="15" t="n">
         <f aca="false">C6/A6</f>
         <v>0.046176318</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="15" t="n">
         <f aca="false">Assumptions!$B$20*Assumptions!$B$5/A6*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.02982446892</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="15" t="n">
         <f aca="false">D6+E6</f>
         <v>0.07600078692</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$14</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="H6" s="18" t="n">
+        <v>2.1654413299476</v>
+      </c>
+      <c r="H6" s="15" t="n">
         <f aca="false">F6+G6</f>
-        <v>1.3758625088676</v>
-      </c>
-      <c r="I6" s="18" t="n">
+        <v>2.2414421168676</v>
+      </c>
+      <c r="I6" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$23</f>
         <v>15.65020000305</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="18" t="n">
         <f aca="false">(I6-H6)/I6</f>
-        <v>0.912086586203405</v>
+        <v>0.856778691874176</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="19" t="n">
         <f aca="false">CEILING(A7/Assumptions!$B$46,1)</f>
         <v>1</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="15" t="n">
         <f aca="false">B7*Assumptions!$B$21*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>4.6176318</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="15" t="n">
         <f aca="false">C7/A7</f>
         <v>0.0092352636</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="15" t="n">
         <f aca="false">Assumptions!$B$20*Assumptions!$B$5/A7*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.005964893784</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="15" t="n">
         <f aca="false">D7+E7</f>
         <v>0.015200157384</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$14</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="H7" s="18" t="n">
+        <v>2.1654413299476</v>
+      </c>
+      <c r="H7" s="15" t="n">
         <f aca="false">F7+G7</f>
-        <v>1.3150618793316</v>
-      </c>
-      <c r="I7" s="18" t="n">
+        <v>2.1806414873316</v>
+      </c>
+      <c r="I7" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$23</f>
         <v>15.65020000305</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="18" t="n">
         <f aca="false">(I7-H7)/I7</f>
-        <v>0.915971560805912</v>
+        <v>0.860663666476683</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="19" t="n">
         <f aca="false">CEILING(A8/Assumptions!$B$46,1)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="15" t="n">
         <f aca="false">B8*Assumptions!$B$21*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>4.6176318</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="15" t="n">
         <f aca="false">C8/A8</f>
         <v>0.0046176318</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="15" t="n">
         <f aca="false">Assumptions!$B$20*Assumptions!$B$5/A8*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.002982446892</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">D8+E8</f>
         <v>0.007600078692</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$14</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="H8" s="18" t="n">
+        <v>2.1654413299476</v>
+      </c>
+      <c r="H8" s="15" t="n">
         <f aca="false">F8+G8</f>
-        <v>1.3074618006396</v>
-      </c>
-      <c r="I8" s="18" t="n">
+        <v>2.1730414086396</v>
+      </c>
+      <c r="I8" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$23</f>
         <v>15.65020000305</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="18" t="n">
         <f aca="false">(I8-H8)/I8</f>
-        <v>0.916457182631225</v>
+        <v>0.861149288301996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="19" t="n">
         <f aca="false">CEILING(A9/Assumptions!$B$46,1)</f>
         <v>3</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="15" t="n">
         <f aca="false">B9*Assumptions!$B$21*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>13.8528954</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="15" t="n">
         <f aca="false">C9/A9</f>
         <v>0.00277057908</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="15" t="n">
         <f aca="false">Assumptions!$B$20*Assumptions!$B$5/A9*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.0005964893784</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">D9+E9</f>
         <v>0.0033670684584</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$14</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="H9" s="18" t="n">
+        <v>2.1654413299476</v>
+      </c>
+      <c r="H9" s="15" t="n">
         <f aca="false">F9+G9</f>
-        <v>1.303228790406</v>
-      </c>
-      <c r="I9" s="18" t="n">
+        <v>2.168808398406</v>
+      </c>
+      <c r="I9" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$23</f>
         <v>15.65020000305</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="18" t="n">
         <f aca="false">(I9-H9)/I9</f>
-        <v>0.916727659061736</v>
+        <v>0.861419764732506</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="19" t="n">
         <f aca="false">CEILING(A10/Assumptions!$B$46,1)</f>
         <v>5</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="15" t="n">
         <f aca="false">B10*Assumptions!$B$21*Assumptions!$B$5*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>23.088159</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="15" t="n">
         <f aca="false">C10/A10</f>
         <v>0.0023088159</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="15" t="n">
         <f aca="false">Assumptions!$B$20*Assumptions!$B$5/A10*(1+Assumptions!$B$50)^Assumptions!$C$49</f>
         <v>0.0002982446892</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">D10+E10</f>
         <v>0.0026070605892</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$14</f>
-        <v>1.2998617219476</v>
-      </c>
-      <c r="H10" s="18" t="n">
+        <v>2.1654413299476</v>
+      </c>
+      <c r="H10" s="15" t="n">
         <f aca="false">F10+G10</f>
-        <v>1.3024687825368</v>
-      </c>
-      <c r="I10" s="18" t="n">
+        <v>2.1680483905368</v>
+      </c>
+      <c r="I10" s="15" t="n">
         <f aca="false">'Per-Family Monthly Cost'!$C$23</f>
         <v>15.65020000305</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">(I10-H10)/I10</f>
-        <v>0.916776221244267</v>
+        <v>0.861468326915038</v>
       </c>
     </row>
   </sheetData>
@@ -2468,7 +2755,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
@@ -2476,202 +2763,226 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="24"/>
+      <c r="A1" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="24"/>
+      <c r="A3" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>137</v>
+      <c r="A4" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>139</v>
+      <c r="A5" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>141</v>
+      <c r="A6" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>143</v>
+      <c r="A7" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>145</v>
+      <c r="A8" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>147</v>
+      <c r="A9" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>148</v>
+      <c r="B10" s="21" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26"/>
-      <c r="B11" s="24"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="24"/>
+      <c r="A12" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>151</v>
+      <c r="A13" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>153</v>
+      <c r="A14" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>155</v>
+      <c r="A15" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>157</v>
+      <c r="A16" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>159</v>
+      <c r="A17" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>161</v>
+      <c r="A18" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>163</v>
+      <c r="A19" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>165</v>
+      <c r="A20" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>167</v>
+      <c r="A21" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>171</v>
+      <c r="A22" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27" t="s">
-        <v>173</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>175</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>177</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>178</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
